--- a/data/Table_A.xlsx
+++ b/data/Table_A.xlsx
@@ -455,8 +455,16 @@
           <t>MCMASTER CARR SUPPLY</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Black-Oxide Alloy Steel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RoHS 3 (2015/863/EU) Compliant</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -469,8 +477,16 @@
           <t>MCMASTER CARR SUPPLY</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Black-Oxide Alloy Steel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RoHS 3 (2015/863/EU) Compliant</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -483,8 +499,16 @@
           <t>MCMASTER CARR SUPPLY</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Black-Oxide Alloy Steel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RoHS 3 (2015/863/EU) Compliant</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -497,8 +521,16 @@
           <t>MCMASTER CARR SUPPLY</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Black-Oxide Alloy Steel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RoHS 3 (2015/863/EU) Compliant</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
